--- a/artfynd/A 60019-2022 artfynd.xlsx
+++ b/artfynd/A 60019-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60019-2022 artfynd.xlsx
+++ b/artfynd/A 60019-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY79"/>
+  <dimension ref="A1:AY78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8693,7 +8693,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>69614355</v>
+        <v>69614329</v>
       </c>
       <c r="B68" t="n">
         <v>88896</v>
@@ -8739,14 +8739,14 @@
       <c r="K68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Blöte. SO om, Upl</t>
+          <t>Blöte, SO om, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>710774.3849942645</v>
+        <v>710797.9978022416</v>
       </c>
       <c r="R68" t="n">
-        <v>6654998.965700288</v>
+        <v>6655025.39743646</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8821,10 +8821,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>69614329</v>
+        <v>69614362</v>
       </c>
       <c r="B69" t="n">
-        <v>88896</v>
+        <v>90645</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8833,25 +8833,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>720</v>
+        <v>4361</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -8871,10 +8871,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>710797.9978022416</v>
+        <v>710755.3203918817</v>
       </c>
       <c r="R69" t="n">
-        <v>6655025.39743646</v>
+        <v>6654945.705376616</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8949,10 +8949,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>69614362</v>
+        <v>69614339</v>
       </c>
       <c r="B70" t="n">
-        <v>90645</v>
+        <v>88896</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8961,25 +8961,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4361</v>
+        <v>720</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8999,10 +8999,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>710755.3203918817</v>
+        <v>710716.5771621495</v>
       </c>
       <c r="R70" t="n">
-        <v>6654945.705376616</v>
+        <v>6655043.316270623</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9077,10 +9077,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>69614339</v>
+        <v>69614357</v>
       </c>
       <c r="B71" t="n">
-        <v>88896</v>
+        <v>90645</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9089,25 +9089,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>720</v>
+        <v>4361</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -9127,10 +9127,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>710716.5771621495</v>
+        <v>710741.2693301686</v>
       </c>
       <c r="R71" t="n">
-        <v>6655043.316270623</v>
+        <v>6654962.961262135</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9205,10 +9205,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>69614357</v>
+        <v>69614332</v>
       </c>
       <c r="B72" t="n">
-        <v>90645</v>
+        <v>88896</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9217,25 +9217,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4361</v>
+        <v>720</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -9255,10 +9255,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>710741.2693301686</v>
+        <v>710686.7403338499</v>
       </c>
       <c r="R72" t="n">
-        <v>6654962.961262135</v>
+        <v>6655029.070320031</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9333,10 +9333,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>69614332</v>
+        <v>69614366</v>
       </c>
       <c r="B73" t="n">
-        <v>88896</v>
+        <v>90671</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9345,25 +9345,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>720</v>
+        <v>4368</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -9383,10 +9383,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>710686.7403338499</v>
+        <v>710755.3203918817</v>
       </c>
       <c r="R73" t="n">
-        <v>6655029.070320031</v>
+        <v>6654945.705376616</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9461,10 +9461,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>69614366</v>
+        <v>69614374</v>
       </c>
       <c r="B74" t="n">
-        <v>90671</v>
+        <v>90661</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9473,25 +9473,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4368</v>
+        <v>2058</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -9511,10 +9511,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>710755.3203918817</v>
+        <v>710799.6443425636</v>
       </c>
       <c r="R74" t="n">
-        <v>6654945.705376616</v>
+        <v>6655040.540524459</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9589,7 +9589,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>69614374</v>
+        <v>69614379</v>
       </c>
       <c r="B75" t="n">
         <v>90661</v>
@@ -9635,14 +9635,14 @@
       <c r="K75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Blöte, SO om, Upl</t>
+          <t>Bornan, SO om, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>710799.6443425636</v>
+        <v>710763.1812392919</v>
       </c>
       <c r="R75" t="n">
-        <v>6655040.540524459</v>
+        <v>6655010.364424504</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9717,10 +9717,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>69614379</v>
+        <v>69614327</v>
       </c>
       <c r="B76" t="n">
-        <v>90661</v>
+        <v>88896</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9733,21 +9733,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2058</v>
+        <v>720</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -9763,14 +9763,14 @@
       <c r="K76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Bornan, SO om, Upl</t>
+          <t>Blöte, SO om, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>710763.1812392919</v>
+        <v>710732.7604936484</v>
       </c>
       <c r="R76" t="n">
-        <v>6655010.364424504</v>
+        <v>6655032.703797887</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9845,7 +9845,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>69614327</v>
+        <v>69614352</v>
       </c>
       <c r="B77" t="n">
         <v>88896</v>
@@ -9895,10 +9895,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>710732.7604936484</v>
+        <v>710757.228285668</v>
       </c>
       <c r="R77" t="n">
-        <v>6655032.703797887</v>
+        <v>6655009.02084529</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9973,10 +9973,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>69614352</v>
+        <v>69614364</v>
       </c>
       <c r="B78" t="n">
-        <v>88896</v>
+        <v>90645</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9985,25 +9985,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>720</v>
+        <v>4361</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -10023,10 +10023,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>710757.228285668</v>
+        <v>710874.8245067496</v>
       </c>
       <c r="R78" t="n">
-        <v>6655009.02084529</v>
+        <v>6654973.607647975</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -10098,134 +10098,6 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>69614364</v>
-      </c>
-      <c r="B79" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>4361</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Orange taggsvamp</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Hydnellum aurantiacum</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Blöte, SO om, Upl</t>
-        </is>
-      </c>
-      <c r="Q79" t="n">
-        <v>710874.8245067496</v>
-      </c>
-      <c r="R79" t="n">
-        <v>6654973.607647975</v>
-      </c>
-      <c r="S79" t="n">
-        <v>5</v>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Norrtälje</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>Väddö</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>2017-09-16</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>2017-09-16</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Exkursion med Stockholms svampvänner och Kristoffer Stighäll</t>
-        </is>
-      </c>
-      <c r="AD79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF79" t="inlineStr"/>
-      <c r="AG79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT79" t="inlineStr"/>
-      <c r="AW79" t="inlineStr">
-        <is>
-          <t>Rasmus Elleby</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>Rasmus Elleby, Jacob Rudhe, Kristoffer Stighäll, Hans von Eichwald, Micael Söderman, Niklas Hjort</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60019-2022 artfynd.xlsx
+++ b/artfynd/A 60019-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY93"/>
+  <dimension ref="A1:AZ93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923469</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/217432</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/226467</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55502319</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55502323</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1317,6 +1347,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55502678</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1422,6 +1457,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55502750</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1535,6 +1575,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67922726</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1648,6 +1693,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923144</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1761,6 +1811,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923164</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1874,6 +1929,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923187</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1987,6 +2047,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923233</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2100,6 +2165,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923266</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2208,6 +2278,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923401</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2321,6 +2396,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923480</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2434,6 +2514,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923527</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2547,6 +2632,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923546</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2660,6 +2750,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923669</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2773,6 +2868,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923956</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2886,6 +2986,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69614327</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2999,6 +3104,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69614329</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3112,6 +3222,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69614332</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3225,6 +3340,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69614339</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3338,6 +3458,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69614343</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3451,6 +3576,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69614347</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3564,6 +3694,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69614352</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3677,6 +3812,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69614355</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3782,6 +3922,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55502738</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3887,6 +4032,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55502747</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3992,6 +4142,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923498</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4097,6 +4252,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55502672</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4203,6 +4363,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/384073</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4308,6 +4473,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55502661</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4417,6 +4587,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923006</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4530,6 +4705,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923157</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4643,6 +4823,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923194</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4756,6 +4941,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923200</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4869,6 +5059,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923218</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4982,6 +5177,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923408</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5095,6 +5295,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923577</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5208,6 +5413,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923900</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5321,6 +5531,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69614369</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5434,6 +5649,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69614370</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5547,6 +5767,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69614374</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5660,6 +5885,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69614378</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5773,6 +6003,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69614379</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5875,6 +6110,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1155006</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5975,6 +6215,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55502752</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6075,6 +6320,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923548</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6180,6 +6430,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923953</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6285,6 +6540,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69614320</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6385,6 +6645,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55502306</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6496,6 +6761,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1156523</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6596,6 +6866,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55502698</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6709,6 +6984,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923474</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6822,6 +7102,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69614357</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6935,6 +7220,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69614362</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7048,6 +7338,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69614364</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7148,6 +7443,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923717</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7259,6 +7559,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1381480</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7359,6 +7664,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55502313</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7464,6 +7774,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67922986</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7564,6 +7879,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923039</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7664,6 +7984,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923210</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7764,6 +8089,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923490</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7864,6 +8194,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923572</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7964,6 +8299,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923687</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8064,6 +8404,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923706</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8164,6 +8509,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923891</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8264,6 +8614,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923945</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8364,6 +8719,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67977454</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8469,6 +8829,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55502694</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8574,6 +8939,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55502743</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8687,6 +9057,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923090</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8800,6 +9175,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923711</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8913,6 +9293,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69614366</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9013,6 +9398,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923595</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9124,6 +9514,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1616400</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9224,6 +9619,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55502702</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9324,6 +9724,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923054</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9424,6 +9829,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923949</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9523,6 +9933,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55502737</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9631,6 +10046,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923924</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9742,6 +10162,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55502311</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9848,6 +10273,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923662</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9948,6 +10378,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55502321</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10053,6 +10488,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923563</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10164,6 +10604,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2643608</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10280,6 +10725,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4047595</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10380,6 +10830,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923553</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10480,6 +10935,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923056</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10580,8 +11040,107 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67923565</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>